--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1038_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1038_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,16 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Grandfather Clocks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Dont Look</t>
         </is>
       </c>
@@ -469,6 +479,12 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.134492814540863</v>
       </c>
     </row>
@@ -486,6 +502,12 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.253706693649292</v>
       </c>
     </row>
@@ -505,6 +527,12 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -522,6 +550,12 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -537,6 +571,12 @@
         <v>0.5578055381774902</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.285605251789093</v>
       </c>
     </row>
@@ -554,6 +594,12 @@
         <v>0.2414050102233887</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.354613870382309</v>
       </c>
     </row>
@@ -571,6 +617,12 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.3016420602798462</v>
       </c>
     </row>
@@ -590,6 +642,12 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -605,6 +663,12 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.5780056118965149</v>
       </c>
     </row>
@@ -624,6 +688,12 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -641,6 +711,12 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -658,6 +734,12 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -675,6 +757,12 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -690,6 +778,12 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.2943075299263</v>
       </c>
     </row>
@@ -709,6 +803,12 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -726,6 +826,12 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -743,6 +849,12 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -760,6 +872,10 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -777,6 +893,10 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -794,6 +914,10 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -809,6 +933,10 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -824,6 +952,10 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -839,6 +971,10 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -850,6 +986,10 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0.1514982432126999</v>
       </c>
     </row>
@@ -863,6 +1003,10 @@
         <v>0.6573362350463867</v>
       </c>
       <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0.1927599906921387</v>
       </c>
     </row>
@@ -876,6 +1020,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0.5580662488937378</v>
       </c>
     </row>
@@ -889,6 +1037,10 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -902,6 +1054,10 @@
         <v>0.06887558847665787</v>
       </c>
       <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0.2678758800029755</v>
       </c>
     </row>
@@ -915,6 +1071,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0.2793696224689484</v>
       </c>
     </row>
@@ -927,7 +1087,9 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0.4956322610378265</v>
       </c>
     </row>
@@ -940,7 +1102,9 @@
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -953,7 +1117,9 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0.5057454109191895</v>
       </c>
     </row>
@@ -966,7 +1132,9 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -979,7 +1147,9 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.5848335027694702</v>
       </c>
     </row>
@@ -992,7 +1162,9 @@
       <c r="D36" t="n">
         <v>0.1099477559328079</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,7 +1177,9 @@
       <c r="D37" t="n">
         <v>0.2094802856445312</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1018,7 +1192,9 @@
       <c r="D38" t="n">
         <v>0.302581399679184</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1031,7 +1207,9 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1044,7 +1222,9 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0.4072491526603699</v>
       </c>
     </row>
@@ -1057,7 +1237,9 @@
       <c r="D41" t="n">
         <v>0.4655124545097351</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0.3246217370033264</v>
       </c>
     </row>
@@ -1070,7 +1252,9 @@
       <c r="D42" t="n">
         <v>0.392194926738739</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0.01382220070809126</v>
       </c>
     </row>
@@ -1084,6 +1268,8 @@
         <v>0</v>
       </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1095,6 +1281,8 @@
         <v>0.2677249312400818</v>
       </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1106,6 +1294,8 @@
         <v>0.4614186584949493</v>
       </c>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1117,6 +1307,8 @@
         <v>0.2740925550460815</v>
       </c>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1128,6 +1320,8 @@
         <v>0.3405221998691559</v>
       </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1139,6 +1333,8 @@
         <v>0.3621982634067535</v>
       </c>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1150,6 +1346,8 @@
         <v>0.3680191040039062</v>
       </c>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1161,6 +1359,8 @@
         <v>0.5348386764526367</v>
       </c>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1172,6 +1372,8 @@
         <v>0</v>
       </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1183,6 +1385,8 @@
         <v>0</v>
       </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1194,6 +1398,8 @@
         <v>0.5306054949760437</v>
       </c>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1205,6 +1411,8 @@
         <v>0</v>
       </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1216,6 +1424,8 @@
         <v>0</v>
       </c>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1227,6 +1437,8 @@
         <v>0</v>
       </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
